--- a/grid_search_results.xlsx
+++ b/grid_search_results.xlsx
@@ -525,13 +525,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5425797503467407</v>
+        <v>0.09596928982725528</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2594625348246477</v>
+        <v>0.0002767769220663037</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4325828720452386</v>
+        <v>0.0217698322869655</v>
       </c>
       <c r="E2" t="n">
         <v>512</v>
@@ -588,13 +588,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5348127600554785</v>
+        <v>0.1010876519513756</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2997474928225223</v>
+        <v>-0.0008889659450104628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3624296251552842</v>
+        <v>0.01935670525671847</v>
       </c>
       <c r="E3" t="n">
         <v>512</v>
@@ -651,13 +651,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3803051317614424</v>
+        <v>0.09852847088931542</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05639552877768399</v>
+        <v>0.0009422785181998746</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1562982172282909</v>
+        <v>0.009427987800815902</v>
       </c>
       <c r="E4" t="n">
         <v>512</v>
@@ -714,7 +714,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -777,13 +777,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.348127600554785</v>
+        <v>0.1740243122200896</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04181098099911783</v>
+        <v>0.07607302846856043</v>
       </c>
       <c r="D6" t="n">
-        <v>0.151775528758727</v>
+        <v>0.321471553531548</v>
       </c>
       <c r="E6" t="n">
         <v>512</v>
@@ -840,13 +840,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3384188626907074</v>
+        <v>0.1753039027511197</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05591092924676634</v>
+        <v>0.07657524241004254</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1504187444531148</v>
+        <v>0.3238743636627453</v>
       </c>
       <c r="E7" t="n">
         <v>512</v>
@@ -903,13 +903,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3472954230235784</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03566548011195344</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1309773275796342</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>512</v>
@@ -966,13 +966,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3528432732316227</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03777256382434961</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1370828285692193</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>512</v>
@@ -1029,13 +1029,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3617198335644938</v>
+        <v>0.2040946896992962</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05573172218230123</v>
+        <v>0.06430320418638408</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1913726238416422</v>
+        <v>0.3152136084574049</v>
       </c>
       <c r="E10" t="n">
         <v>512</v>
@@ -1092,13 +1092,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3739251040221914</v>
+        <v>0.1017274472168906</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01844432990231434</v>
+        <v>-0.001440250262788829</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1209113352494332</v>
+        <v>0.01075233176548406</v>
       </c>
       <c r="E11" t="n">
         <v>512</v>
@@ -1155,13 +1155,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5090152565880721</v>
+        <v>0.127319257837492</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1851425353623287</v>
+        <v>0.01076414375062002</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3587910452309826</v>
+        <v>0.04239114668923969</v>
       </c>
       <c r="E12" t="n">
         <v>512</v>
@@ -1218,13 +1218,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4915395284327323</v>
+        <v>0.1676263595649392</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1479826486404634</v>
+        <v>0.0666315924155902</v>
       </c>
       <c r="D13" t="n">
-        <v>0.294673528788898</v>
+        <v>0.2236558292314406</v>
       </c>
       <c r="E13" t="n">
         <v>512</v>
@@ -1281,13 +1281,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09916826615483046</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.0001561977126814028</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.04732048933598984</v>
       </c>
       <c r="E14" t="n">
         <v>512</v>
@@ -1344,13 +1344,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09085092770313499</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.0005324356784239293</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.0452486366024336</v>
       </c>
       <c r="E15" t="n">
         <v>512</v>
@@ -1407,13 +1407,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09404990403071017</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0.0003901539496568099</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.04375160853033183</v>
       </c>
       <c r="E16" t="n">
         <v>512</v>
@@ -1470,7 +1470,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1023672424824056</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.001521222363558808</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.04921554448962222</v>
       </c>
       <c r="E18" t="n">
         <v>512</v>
@@ -1596,13 +1596,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09085092770313499</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.0006430194407102545</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.04765257449968886</v>
       </c>
       <c r="E19" t="n">
         <v>512</v>
@@ -1659,13 +1659,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-0.0001253080902706412</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.04922291240106103</v>
       </c>
       <c r="E20" t="n">
         <v>512</v>
@@ -1722,13 +1722,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09724888035828536</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.00192087257086606</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.05469455964891262</v>
       </c>
       <c r="E21" t="n">
         <v>512</v>
@@ -1785,13 +1785,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1445937300063979</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.0353000748671807</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.1887245852904072</v>
       </c>
       <c r="E22" t="n">
         <v>512</v>
@@ -1848,13 +1848,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1132437619961612</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.007894555980871165</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.07503985762363027</v>
       </c>
       <c r="E23" t="n">
         <v>512</v>
@@ -1911,7 +1911,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2037,13 +2037,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5905686546463246</v>
+        <v>0.1362763915547025</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3357080417428412</v>
+        <v>0.008333808121633151</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5044164489747343</v>
+        <v>0.09352471037402199</v>
       </c>
       <c r="E26" t="n">
         <v>512</v>
@@ -2100,13 +2100,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09852847088931542</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0.000379491224728603</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.002731940701116744</v>
       </c>
       <c r="E27" t="n">
         <v>512</v>
@@ -2163,13 +2163,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09085092770313499</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-0.000962404830506502</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.002458916218271924</v>
       </c>
       <c r="E28" t="n">
         <v>512</v>
@@ -2226,7 +2226,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8238557558945908</v>
+        <v>0.1778630838131798</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7328125356545562</v>
+        <v>0.101292183651198</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7259709959346158</v>
+        <v>0.3169443068682156</v>
       </c>
       <c r="E30" t="n">
         <v>512</v>
@@ -2352,13 +2352,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.7509015256588072</v>
+        <v>0.1695457453614843</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5811176303299448</v>
+        <v>0.1247712080772979</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6531908939834685</v>
+        <v>0.3448614638498956</v>
       </c>
       <c r="E31" t="n">
         <v>512</v>
@@ -2415,13 +2415,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.743134535367545</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5649601112671681</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6403550330543994</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>512</v>
@@ -2478,13 +2478,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7486823855755894</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5610451492601954</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6315036500990099</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>512</v>
@@ -2541,13 +2541,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.5337031900138697</v>
+        <v>0.09596928982725528</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3710820045026665</v>
+        <v>-8.994910323018718e-06</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4863634355848471</v>
+        <v>0.007358657119914663</v>
       </c>
       <c r="E34" t="n">
         <v>512</v>
@@ -2604,13 +2604,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.5389736477115118</v>
+        <v>0.1746641074856046</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4082085718089242</v>
+        <v>0.1139367535793771</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5154183497664973</v>
+        <v>0.3696647635633195</v>
       </c>
       <c r="E35" t="n">
         <v>512</v>
@@ -2667,13 +2667,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5414701803051317</v>
+        <v>0.1106845809341011</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2522694433343159</v>
+        <v>0.004100479592386603</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4259438481463931</v>
+        <v>0.05212229721354063</v>
       </c>
       <c r="E36" t="n">
         <v>512</v>
@@ -2730,13 +2730,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.7522884882108183</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5855234522194855</v>
+        <v>8.370436342434254e-06</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6736657577611892</v>
+        <v>0.0028479388176342</v>
       </c>
       <c r="E37" t="n">
         <v>512</v>
@@ -2793,13 +2793,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.3165048543689321</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0040364121016259</v>
+        <v>4.29067962272563e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01274144495457633</v>
+        <v>0.001372575118237456</v>
       </c>
       <c r="E38" t="n">
         <v>512</v>
@@ -2856,7 +2856,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3045,13 +3045,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1081830790568655</v>
+        <v>0.09724888035828536</v>
       </c>
       <c r="C42" t="n">
-        <v>0.003054997327606521</v>
+        <v>0.001549295734919876</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01661318233059905</v>
+        <v>0.05615007520997459</v>
       </c>
       <c r="E42" t="n">
         <v>512</v>
@@ -3108,13 +3108,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1151178918169209</v>
+        <v>0.1030070377479207</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003612534859252068</v>
+        <v>0.003068548083166589</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01513156239102087</v>
+        <v>0.05668142301991716</v>
       </c>
       <c r="E43" t="n">
         <v>512</v>
@@ -3171,13 +3171,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1128987517337032</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C44" t="n">
-        <v>0.004529241678153586</v>
+        <v>0.0006500995087410946</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01746553097315317</v>
+        <v>0.04883709145392471</v>
       </c>
       <c r="E44" t="n">
         <v>512</v>
@@ -3234,13 +3234,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1353675450762829</v>
+        <v>0.1017274472168906</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01296533040089146</v>
+        <v>0.002837764428645241</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02814569303522921</v>
+        <v>0.05430510233172118</v>
       </c>
       <c r="E45" t="n">
         <v>512</v>
@@ -3297,13 +3297,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6357836338418863</v>
+        <v>0.1426743442098528</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4891455002689592</v>
+        <v>0.04773803085754751</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4139094926176557</v>
+        <v>0.1330612566220924</v>
       </c>
       <c r="E46" t="n">
         <v>512</v>
@@ -3360,13 +3360,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.3564493758668516</v>
+        <v>0.1074856046065259</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1047257717572857</v>
+        <v>0.0002316090304985399</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1447783583598601</v>
+        <v>0.05122152112255793</v>
       </c>
       <c r="E47" t="n">
         <v>512</v>
@@ -3423,13 +3423,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.4554785020804438</v>
+        <v>0.1074856046065259</v>
       </c>
       <c r="C48" t="n">
-        <v>0.09737158224346971</v>
+        <v>0.005063084395454331</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2364485255722659</v>
+        <v>0.0537027849962252</v>
       </c>
       <c r="E48" t="n">
         <v>512</v>
@@ -3486,7 +3486,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -3549,13 +3549,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1872399445214979</v>
+        <v>0.1567498400511836</v>
       </c>
       <c r="C50" t="n">
-        <v>0.005645793069401869</v>
+        <v>0.05697613355726755</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0174296411412597</v>
+        <v>0.280570611466011</v>
       </c>
       <c r="E50" t="n">
         <v>512</v>
@@ -3612,13 +3612,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.3436893203883495</v>
+        <v>0.09213051823416507</v>
       </c>
       <c r="C51" t="n">
-        <v>0.03349382177099112</v>
+        <v>-0.001096777776748299</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1196428645345208</v>
+        <v>0.004369938929449126</v>
       </c>
       <c r="E51" t="n">
         <v>512</v>
@@ -3675,13 +3675,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>-0.0004758061252005585</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.003791822418516138</v>
       </c>
       <c r="E52" t="n">
         <v>512</v>
@@ -3738,13 +3738,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3531206657420249</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C53" t="n">
-        <v>0.05185936438945347</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1689832718442177</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>512</v>
@@ -3801,13 +3801,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.3786407766990291</v>
+        <v>0.1554702495201536</v>
       </c>
       <c r="C54" t="n">
-        <v>0.05003410225485453</v>
+        <v>0.08531548471475692</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1821799114964218</v>
+        <v>0.2826503009920078</v>
       </c>
       <c r="E54" t="n">
         <v>512</v>
@@ -3864,13 +3864,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.3547850208044383</v>
+        <v>0.1522712731925784</v>
       </c>
       <c r="C55" t="n">
-        <v>0.04754932151424787</v>
+        <v>0.07718387352400995</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1557327952288541</v>
+        <v>0.3285576696202331</v>
       </c>
       <c r="E55" t="n">
         <v>512</v>
@@ -3927,13 +3927,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.4091539528432732</v>
+        <v>0.1522712731925784</v>
       </c>
       <c r="C56" t="n">
-        <v>0.07030815056898708</v>
+        <v>0.0771167674262138</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1594857767505289</v>
+        <v>0.325481009036882</v>
       </c>
       <c r="E56" t="n">
         <v>512</v>
@@ -3990,13 +3990,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.3497919556171983</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C57" t="n">
-        <v>0.05212488599292955</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1485458291597236</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>512</v>
@@ -4053,13 +4053,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.4108183079056865</v>
+        <v>0.1669865642994242</v>
       </c>
       <c r="C58" t="n">
-        <v>0.05064430971348941</v>
+        <v>0.0842020309933198</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1394433132039063</v>
+        <v>0.2586955833775835</v>
       </c>
       <c r="E58" t="n">
         <v>512</v>
@@ -4116,13 +4116,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.5919556171983357</v>
+        <v>0.1906589891234805</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4188370011771376</v>
+        <v>0.07931179181447397</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4997990647191342</v>
+        <v>0.2988900308676128</v>
       </c>
       <c r="E59" t="n">
         <v>512</v>
@@ -4179,13 +4179,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.3581137309292649</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C60" t="n">
-        <v>0.05174564013693957</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1761004223868496</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>512</v>
@@ -4242,13 +4242,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3423023578363384</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C61" t="n">
-        <v>0.001031196971771016</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.04476220585287973</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>512</v>
@@ -4305,7 +4305,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -4557,13 +4557,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09724888035828536</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.0008091334978569238</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.04971318475380249</v>
       </c>
       <c r="E66" t="n">
         <v>512</v>
@@ -4620,13 +4620,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>-0.0001483156496768699</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>0.0473898515278821</v>
       </c>
       <c r="E67" t="n">
         <v>512</v>
@@ -4683,13 +4683,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09788867562380038</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.001981123033119173</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>0.05520958281325107</v>
       </c>
       <c r="E68" t="n">
         <v>512</v>
@@ -4746,13 +4746,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09852847088931542</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>0.002855455465136987</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>0.05397784278008055</v>
       </c>
       <c r="E69" t="n">
         <v>512</v>
@@ -4809,13 +4809,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1362763915547025</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>0.04248494713020061</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>0.2245514000644394</v>
       </c>
       <c r="E70" t="n">
         <v>512</v>
@@ -4872,7 +4872,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -5061,13 +5061,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.5384188626907074</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3979137492194778</v>
+        <v>0.0002954068497384131</v>
       </c>
       <c r="D74" t="n">
-        <v>0.490967750818642</v>
+        <v>0.004392020426430676</v>
       </c>
       <c r="E74" t="n">
         <v>512</v>
@@ -5124,13 +5124,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.5420249653259362</v>
+        <v>0.09660908509277032</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2577342359120987</v>
+        <v>4.631315107756874e-05</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4224575761706461</v>
+        <v>0.007467289272947402</v>
       </c>
       <c r="E75" t="n">
         <v>512</v>
@@ -5187,13 +5187,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09660908509277032</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>-0.0001881782875547436</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>0.004194183875001306</v>
       </c>
       <c r="E76" t="n">
         <v>512</v>
@@ -5250,7 +5250,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -5313,13 +5313,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.79251040221914</v>
+        <v>0.1708253358925144</v>
       </c>
       <c r="C78" t="n">
-        <v>0.7580669467540875</v>
+        <v>0.1004774839733135</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7336059924036981</v>
+        <v>0.3317411564139085</v>
       </c>
       <c r="E78" t="n">
         <v>512</v>
@@ -5376,13 +5376,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.541747572815534</v>
+        <v>0.1746641074856046</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2578272456595654</v>
+        <v>0.1139367535793771</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4212306696538777</v>
+        <v>0.3696647635633195</v>
       </c>
       <c r="E79" t="n">
         <v>512</v>
@@ -5439,13 +5439,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.5445214979195562</v>
+        <v>0.1746641074856046</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2620341738715714</v>
+        <v>0.1139367535793771</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4282423930399054</v>
+        <v>0.3696647635633195</v>
       </c>
       <c r="E80" t="n">
         <v>512</v>
@@ -5502,13 +5502,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.7511789181692095</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C81" t="n">
-        <v>0.643444367735551</v>
+        <v>-0.00118931521524044</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6885680993951114</v>
+        <v>0.004005188662454246</v>
       </c>
       <c r="E81" t="n">
         <v>512</v>
@@ -5565,13 +5565,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.5386962552011095</v>
+        <v>0.1023672424824056</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3975037215008993</v>
+        <v>-0.0004181467982117384</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4982145066480044</v>
+        <v>0.009427297325306585</v>
       </c>
       <c r="E82" t="n">
         <v>512</v>
@@ -5628,13 +5628,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.5414701803051317</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2574356406312951</v>
+        <v>1.243557890322163e-05</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4212304482482515</v>
+        <v>0.002156100648172443</v>
       </c>
       <c r="E83" t="n">
         <v>512</v>
@@ -5691,7 +5691,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -5754,13 +5754,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09404990403071017</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>-0.0003754003060646959</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>0.002568747802259971</v>
       </c>
       <c r="E85" t="n">
         <v>512</v>
@@ -5817,13 +5817,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1023672424824056</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>-0.004578486094516481</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.06613500010446866</v>
       </c>
       <c r="E86" t="n">
         <v>512</v>
@@ -5880,7 +5880,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -6069,13 +6069,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.1339805825242718</v>
+        <v>0.1151631477927063</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0109963016008191</v>
+        <v>0.006986166490544562</v>
       </c>
       <c r="D90" t="n">
-        <v>0.03102996009144534</v>
+        <v>0.06414241032240942</v>
       </c>
       <c r="E90" t="n">
         <v>512</v>
@@ -6132,13 +6132,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.119001386962552</v>
+        <v>0.1010876519513756</v>
       </c>
       <c r="C91" t="n">
-        <v>0.005479295725728703</v>
+        <v>0.004408080158653659</v>
       </c>
       <c r="D91" t="n">
-        <v>0.01796403398096011</v>
+        <v>0.05757049607027515</v>
       </c>
       <c r="E91" t="n">
         <v>512</v>
@@ -6195,13 +6195,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1251040221914008</v>
+        <v>0.1017274472168906</v>
       </c>
       <c r="C92" t="n">
-        <v>0.01007682851808943</v>
+        <v>0.001578581051268896</v>
       </c>
       <c r="D92" t="n">
-        <v>0.02379591026941242</v>
+        <v>0.05376162634818067</v>
       </c>
       <c r="E92" t="n">
         <v>512</v>
@@ -6258,13 +6258,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3361997226074896</v>
+        <v>0.09788867562380038</v>
       </c>
       <c r="C93" t="n">
-        <v>0.242818261135114</v>
+        <v>0.002059907223933865</v>
       </c>
       <c r="D93" t="n">
-        <v>0.199116230483777</v>
+        <v>0.05720633480711793</v>
       </c>
       <c r="E93" t="n">
         <v>512</v>
@@ -6321,13 +6321,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.3977808599167822</v>
+        <v>0.1426743442098528</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2695834322893298</v>
+        <v>0.02804162057343982</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3231347279707001</v>
+        <v>0.1428279491514424</v>
       </c>
       <c r="E94" t="n">
         <v>512</v>
@@ -6384,13 +6384,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.3694868238557559</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C95" t="n">
-        <v>0.118064513182651</v>
+        <v>0.0001136268218026025</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1523846037655208</v>
+        <v>0.002330795889308598</v>
       </c>
       <c r="E95" t="n">
         <v>512</v>
@@ -6447,7 +6447,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.3325936199722607</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C98" t="n">
-        <v>0.02048079316965968</v>
+        <v>-0.001138248357790919</v>
       </c>
       <c r="D98" t="n">
-        <v>0.08558729727280938</v>
+        <v>0.01882568240567409</v>
       </c>
       <c r="E98" t="n">
         <v>1024</v>
@@ -6636,13 +6636,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.312621359223301</v>
+        <v>0.09916826615483046</v>
       </c>
       <c r="C99" t="n">
-        <v>4.049120389727212e-05</v>
+        <v>0.0003231848133139998</v>
       </c>
       <c r="D99" t="n">
-        <v>0.003720271933399976</v>
+        <v>0.01364571494396003</v>
       </c>
       <c r="E99" t="n">
         <v>1024</v>
@@ -6699,13 +6699,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.3611650485436893</v>
+        <v>0.09596928982725528</v>
       </c>
       <c r="C100" t="n">
-        <v>0.01993877655436641</v>
+        <v>-0.0001121680974940517</v>
       </c>
       <c r="D100" t="n">
-        <v>0.06623064470058147</v>
+        <v>0.003086417360218831</v>
       </c>
       <c r="E100" t="n">
         <v>1024</v>
@@ -6762,7 +6762,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -6825,13 +6825,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0.350624133148405</v>
+        <v>0.1753039027511197</v>
       </c>
       <c r="C102" t="n">
-        <v>0.05270663446996716</v>
+        <v>0.0872187213626151</v>
       </c>
       <c r="D102" t="n">
-        <v>0.1497034686515308</v>
+        <v>0.312522806367837</v>
       </c>
       <c r="E102" t="n">
         <v>1024</v>
@@ -6888,13 +6888,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0.3547850208044383</v>
+        <v>0.1740243122200896</v>
       </c>
       <c r="C103" t="n">
-        <v>0.04694183827481826</v>
+        <v>0.07607302846856043</v>
       </c>
       <c r="D103" t="n">
-        <v>0.1533194847253992</v>
+        <v>0.321471553531548</v>
       </c>
       <c r="E103" t="n">
         <v>1024</v>
@@ -6951,13 +6951,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0.3547850208044383</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04714667624295627</v>
+        <v>-1.307350769741684e-05</v>
       </c>
       <c r="D104" t="n">
-        <v>0.1537595581588402</v>
+        <v>0.002480706928332225</v>
       </c>
       <c r="E104" t="n">
         <v>1024</v>
@@ -7014,13 +7014,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0.3547850208044383</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C105" t="n">
-        <v>0.04726352147079127</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.1570547463693625</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>1024</v>
@@ -7077,13 +7077,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0.536754507628294</v>
+        <v>0.1964171465131158</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3443902146815377</v>
+        <v>0.08718448958559258</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4470552335316563</v>
+        <v>0.3210604492051166</v>
       </c>
       <c r="E106" t="n">
         <v>1024</v>
@@ -7140,7 +7140,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -7203,13 +7203,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1938579654510557</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>0.08895345540257983</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>0.3211679985484941</v>
       </c>
       <c r="E108" t="n">
         <v>1024</v>
@@ -7266,7 +7266,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -7392,13 +7392,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1017274472168906</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>-0.002113142421580121</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>0.0438095341787204</v>
       </c>
       <c r="E111" t="n">
         <v>1024</v>
@@ -7455,13 +7455,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09788867562380038</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>0.0007399095007001428</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>0.04679988049452936</v>
       </c>
       <c r="E112" t="n">
         <v>1024</v>
@@ -7518,7 +7518,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -7581,13 +7581,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1042866282789507</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>0.005239558660705568</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>0.06532256513272282</v>
       </c>
       <c r="E114" t="n">
         <v>1024</v>
@@ -7644,13 +7644,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1036468330134357</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>0.005415605663714329</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>0.06401310809068922</v>
       </c>
       <c r="E115" t="n">
         <v>1024</v>
@@ -7707,13 +7707,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1062060140754958</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>0.004303042551855255</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>0.064840712464056</v>
       </c>
       <c r="E116" t="n">
         <v>1024</v>
@@ -7770,13 +7770,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1305182341650672</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>0.01817934721636862</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>0.08985556376547897</v>
       </c>
       <c r="E117" t="n">
         <v>1024</v>
@@ -7833,13 +7833,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1010876519513756</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>0.001805370265674422</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>0.0265753064176251</v>
       </c>
       <c r="E118" t="n">
         <v>1024</v>
@@ -7896,7 +7896,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -7959,7 +7959,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -8022,7 +8022,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -8085,13 +8085,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>0.5156726768377253</v>
+        <v>0.09341010876519514</v>
       </c>
       <c r="C122" t="n">
-        <v>0.27708413662263</v>
+        <v>-0.0008817491151608016</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4280800974949667</v>
+        <v>0.004765734185195362</v>
       </c>
       <c r="E122" t="n">
         <v>1024</v>
@@ -8148,13 +8148,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0.354507628294036</v>
+        <v>0.09660908509277032</v>
       </c>
       <c r="C123" t="n">
-        <v>0.04492342864730919</v>
+        <v>0.000844290917001466</v>
       </c>
       <c r="D123" t="n">
-        <v>0.1615154377046818</v>
+        <v>0.008964039887692924</v>
       </c>
       <c r="E123" t="n">
         <v>1024</v>
@@ -8211,13 +8211,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0.5392510402219141</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2447382880504426</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4214382625988908</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
         <v>1024</v>
@@ -8274,13 +8274,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0.354507628294036</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C125" t="n">
-        <v>0.04492342864730919</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1615154377046818</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>1024</v>
@@ -8337,13 +8337,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0.537864077669903</v>
+        <v>0.2335252719129878</v>
       </c>
       <c r="C126" t="n">
-        <v>0.4060063877295341</v>
+        <v>0.1994010632431018</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4973299014388021</v>
+        <v>0.4698156721228237</v>
       </c>
       <c r="E126" t="n">
         <v>1024</v>
@@ -8400,13 +8400,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0.5431345353675451</v>
+        <v>0.1420345489443378</v>
       </c>
       <c r="C127" t="n">
-        <v>0.4061545353259466</v>
+        <v>0.07094300495568899</v>
       </c>
       <c r="D127" t="n">
-        <v>0.5008141367936184</v>
+        <v>0.2605078993130152</v>
       </c>
       <c r="E127" t="n">
         <v>1024</v>
@@ -8463,13 +8463,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0.3212205270457698</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C128" t="n">
-        <v>0.005931206986168569</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.00935937826358227</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
         <v>1024</v>
@@ -8526,13 +8526,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1618682021753039</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>0.04383734502925937</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>0.2126795625652579</v>
       </c>
       <c r="E129" t="n">
         <v>1024</v>
@@ -8589,13 +8589,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0.3547850208044383</v>
+        <v>0.1861804222648752</v>
       </c>
       <c r="C130" t="n">
-        <v>0.04742889407715963</v>
+        <v>0.1364055135143216</v>
       </c>
       <c r="D130" t="n">
-        <v>0.156864556786517</v>
+        <v>0.3574638773625559</v>
       </c>
       <c r="E130" t="n">
         <v>1024</v>
@@ -8652,13 +8652,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0.5400832177531206</v>
+        <v>0.1497120921305182</v>
       </c>
       <c r="C131" t="n">
-        <v>0.2943104055128052</v>
+        <v>0.0750818698907509</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4297244353259185</v>
+        <v>0.2991809231712282</v>
       </c>
       <c r="E131" t="n">
         <v>1024</v>
@@ -8715,13 +8715,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>0.3547850208044383</v>
+        <v>0.09532949456174024</v>
       </c>
       <c r="C132" t="n">
-        <v>0.04550734092684989</v>
+        <v>-5.642045809735046e-05</v>
       </c>
       <c r="D132" t="n">
-        <v>0.163126722333652</v>
+        <v>0.001105137287472757</v>
       </c>
       <c r="E132" t="n">
         <v>1024</v>
@@ -8778,7 +8778,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -8841,7 +8841,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -8904,7 +8904,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -9030,7 +9030,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -9093,13 +9093,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>0.1309292649098474</v>
+        <v>0.09724888035828536</v>
       </c>
       <c r="C138" t="n">
-        <v>0.01087729395899614</v>
+        <v>0.0003480752743924517</v>
       </c>
       <c r="D138" t="n">
-        <v>0.02508157425911247</v>
+        <v>0.05227310035770203</v>
       </c>
       <c r="E138" t="n">
         <v>1024</v>
@@ -9156,13 +9156,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>0.1206657420249653</v>
+        <v>0.1062060140754958</v>
       </c>
       <c r="C139" t="n">
-        <v>0.005958637724550874</v>
+        <v>0.005321250094469089</v>
       </c>
       <c r="D139" t="n">
-        <v>0.02172850697167972</v>
+        <v>0.06054719987695638</v>
       </c>
       <c r="E139" t="n">
         <v>1024</v>
@@ -9219,13 +9219,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>0.1306518723994452</v>
+        <v>0.1017274472168906</v>
       </c>
       <c r="C140" t="n">
-        <v>0.008228950921175012</v>
+        <v>0.003162794952611086</v>
       </c>
       <c r="D140" t="n">
-        <v>0.02376099203342974</v>
+        <v>0.0592707185213236</v>
       </c>
       <c r="E140" t="n">
         <v>1024</v>
@@ -9282,13 +9282,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>0.3251040221914008</v>
+        <v>0.1042866282789507</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1060261026950299</v>
+        <v>0.003542821778219251</v>
       </c>
       <c r="D141" t="n">
-        <v>0.1199745385060856</v>
+        <v>0.05773671934446013</v>
       </c>
       <c r="E141" t="n">
         <v>1024</v>
@@ -9345,13 +9345,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>0.5337031900138697</v>
+        <v>0.182341650671785</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4592562344537597</v>
+        <v>0.08819849628466628</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4680153214462131</v>
+        <v>0.2308015184321608</v>
       </c>
       <c r="E142" t="n">
         <v>1024</v>
@@ -9408,13 +9408,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>0.3198335644937587</v>
+        <v>0.1023672424824056</v>
       </c>
       <c r="C143" t="n">
-        <v>0.01369855665836017</v>
+        <v>0.0001191228328216377</v>
       </c>
       <c r="D143" t="n">
-        <v>0.03625034664600141</v>
+        <v>0.02471157726902788</v>
       </c>
       <c r="E143" t="n">
         <v>1024</v>
@@ -9471,7 +9471,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -9597,13 +9597,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>0.5009708737864078</v>
+        <v>0.1074856046065259</v>
       </c>
       <c r="C146" t="n">
-        <v>0.2114614406252194</v>
+        <v>0.002011618971426529</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3745213726056086</v>
+        <v>0.02648482822544444</v>
       </c>
       <c r="E146" t="n">
         <v>1024</v>
@@ -9660,13 +9660,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0.3988904299583911</v>
+        <v>0.09404990403071017</v>
       </c>
       <c r="C147" t="n">
-        <v>0.02390092328911518</v>
+        <v>-0.001828024330631397</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1188846970185296</v>
+        <v>0.01214832888268237</v>
       </c>
       <c r="E147" t="n">
         <v>1024</v>
@@ -9723,13 +9723,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0.3542302357836338</v>
+        <v>0.09596928982725528</v>
       </c>
       <c r="C148" t="n">
-        <v>0.04455428064838228</v>
+        <v>0.002269475856411305</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1599996956827019</v>
+        <v>0.006108071210892983</v>
       </c>
       <c r="E148" t="n">
         <v>1024</v>
@@ -9786,13 +9786,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0.3137309292649099</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.0001151957337476854</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0.001168325199667371</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>1024</v>
@@ -9849,13 +9849,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0.3633841886269071</v>
+        <v>0.1746641074856046</v>
       </c>
       <c r="C150" t="n">
-        <v>0.05366706265724409</v>
+        <v>0.07683586892593938</v>
       </c>
       <c r="D150" t="n">
-        <v>0.1773834441616355</v>
+        <v>0.3249066123756734</v>
       </c>
       <c r="E150" t="n">
         <v>1024</v>
@@ -9912,13 +9912,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0.359500693481276</v>
+        <v>0.1561100447856686</v>
       </c>
       <c r="C151" t="n">
-        <v>0.04886714842232642</v>
+        <v>0.06242937198554001</v>
       </c>
       <c r="D151" t="n">
-        <v>0.1631647399111024</v>
+        <v>0.1971775674681873</v>
       </c>
       <c r="E151" t="n">
         <v>1024</v>
@@ -9975,13 +9975,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>0.3711511789181692</v>
+        <v>0.1324376199616123</v>
       </c>
       <c r="C152" t="n">
-        <v>0.05242520075238643</v>
+        <v>0.01026328180992712</v>
       </c>
       <c r="D152" t="n">
-        <v>0.1504167721033405</v>
+        <v>0.08691992199932413</v>
       </c>
       <c r="E152" t="n">
         <v>1024</v>
@@ -10038,13 +10038,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0.3914008321775312</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C153" t="n">
-        <v>0.08979867753590438</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1941490253089926</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>1024</v>
@@ -10101,13 +10101,13 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>0.3572815533980582</v>
+        <v>0.09724888035828536</v>
       </c>
       <c r="C154" t="n">
-        <v>0.04945324731497729</v>
+        <v>-0.00104955414378266</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1745805603817405</v>
+        <v>0.01361603732931044</v>
       </c>
       <c r="E154" t="n">
         <v>1024</v>
@@ -10164,13 +10164,13 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>0.3542302357836338</v>
+        <v>0.1151631477927063</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0464829111426758</v>
+        <v>0.009257003304483142</v>
       </c>
       <c r="D155" t="n">
-        <v>0.149034948641919</v>
+        <v>0.093594452433992</v>
       </c>
       <c r="E155" t="n">
         <v>1024</v>
@@ -10227,13 +10227,13 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>0.3425797503467407</v>
+        <v>0.1004478566858605</v>
       </c>
       <c r="C156" t="n">
-        <v>0.02857122229852505</v>
+        <v>0.001144007015418357</v>
       </c>
       <c r="D156" t="n">
-        <v>0.09899165748209521</v>
+        <v>0.004235033010945181</v>
       </c>
       <c r="E156" t="n">
         <v>1024</v>
@@ -10290,7 +10290,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -10353,13 +10353,13 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1030070377479207</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>-0.004049049650243153</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>0.07054429664534835</v>
       </c>
       <c r="E158" t="n">
         <v>1024</v>
@@ -10416,7 +10416,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -10479,7 +10479,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -10542,7 +10542,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -10605,13 +10605,13 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09980806142034548</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>0.001910744773252</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>0.05498634244761724</v>
       </c>
       <c r="E162" t="n">
         <v>1024</v>
@@ -10668,13 +10668,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1036468330134357</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>0.003795299908958407</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>0.06066489145441794</v>
       </c>
       <c r="E163" t="n">
         <v>1024</v>
@@ -10731,13 +10731,13 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09724888035828536</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>0.001146352835106179</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>0.04966495453101342</v>
       </c>
       <c r="E164" t="n">
         <v>1024</v>
@@ -10794,13 +10794,13 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1062060140754958</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>0.003786894618236573</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>0.05575157599828485</v>
       </c>
       <c r="E165" t="n">
         <v>1024</v>
@@ -10857,13 +10857,13 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1618682021753039</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>0.04966905274854037</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>0.2164988810030865</v>
       </c>
       <c r="E166" t="n">
         <v>1024</v>
@@ -10920,7 +10920,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -11046,7 +11046,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -11109,13 +11109,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>0.536754507628294</v>
+        <v>0.09852847088931542</v>
       </c>
       <c r="C170" t="n">
-        <v>0.3509904093063761</v>
+        <v>-7.337484089744886e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4345259839723098</v>
+        <v>0.01125211009120648</v>
       </c>
       <c r="E170" t="n">
         <v>1024</v>
@@ -11172,13 +11172,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>0.5395284327323162</v>
+        <v>0.09213051823416507</v>
       </c>
       <c r="C171" t="n">
-        <v>0.3677381245238276</v>
+        <v>9.885703511450147e-05</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4777706258729088</v>
+        <v>0.00499694219281253</v>
       </c>
       <c r="E171" t="n">
         <v>1024</v>
@@ -11235,13 +11235,13 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09788867562380038</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>-0.0005898206388026051</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>0.01168414955912543</v>
       </c>
       <c r="E172" t="n">
         <v>1024</v>
@@ -11298,13 +11298,13 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09660908509277032</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>0.0001279971707664574</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>0.004402465437621489</v>
       </c>
       <c r="E173" t="n">
         <v>1024</v>
@@ -11361,13 +11361,13 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>0.5847434119278779</v>
+        <v>0.182341650671785</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3857375013395078</v>
+        <v>0.1193875449641306</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4798987993991084</v>
+        <v>0.3253647939804188</v>
       </c>
       <c r="E174" t="n">
         <v>1024</v>
@@ -11424,13 +11424,13 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>0.545631067961165</v>
+        <v>0.1772232885476648</v>
       </c>
       <c r="C175" t="n">
-        <v>0.416771650299468</v>
+        <v>0.1152766000328957</v>
       </c>
       <c r="D175" t="n">
-        <v>0.5316739297884395</v>
+        <v>0.3743631802108728</v>
       </c>
       <c r="E175" t="n">
         <v>1024</v>
@@ -11487,13 +11487,13 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.1740243122200896</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>0.1133631122406161</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>0.362606676153598</v>
       </c>
       <c r="E176" t="n">
         <v>1024</v>
@@ -11550,7 +11550,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -11613,13 +11613,13 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>0.5309292649098475</v>
+        <v>0.09788867562380038</v>
       </c>
       <c r="C178" t="n">
-        <v>0.2909264316806119</v>
+        <v>-0.0005893601241663944</v>
       </c>
       <c r="D178" t="n">
-        <v>0.406341956904425</v>
+        <v>0.01299795589942436</v>
       </c>
       <c r="E178" t="n">
         <v>1024</v>
@@ -11676,13 +11676,13 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>0.5384188626907074</v>
+        <v>0.1049264235444658</v>
       </c>
       <c r="C179" t="n">
-        <v>0.294159239834601</v>
+        <v>-6.641864905631834e-05</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4160934316416131</v>
+        <v>0.00896866704778003</v>
       </c>
       <c r="E179" t="n">
         <v>1024</v>
@@ -11739,13 +11739,13 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>0.431622746185853</v>
+        <v>0.0927703134996801</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1881465476791247</v>
+        <v>-0.0004509371191713746</v>
       </c>
       <c r="D180" t="n">
-        <v>0.3923110218406903</v>
+        <v>0.002284458645390057</v>
       </c>
       <c r="E180" t="n">
         <v>1024</v>
@@ -11802,7 +11802,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -11865,7 +11865,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -12054,7 +12054,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -12117,13 +12117,13 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>0.116504854368932</v>
+        <v>0.09724888035828536</v>
       </c>
       <c r="C186" t="n">
-        <v>0.003898557051096917</v>
+        <v>0.002088218857579843</v>
       </c>
       <c r="D186" t="n">
-        <v>0.01783056840138473</v>
+        <v>0.055219635235249</v>
       </c>
       <c r="E186" t="n">
         <v>1024</v>
@@ -12180,13 +12180,13 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>0.1173370319001387</v>
+        <v>0.1004478566858605</v>
       </c>
       <c r="C187" t="n">
-        <v>0.005753236169090693</v>
+        <v>0.002288180100362257</v>
       </c>
       <c r="D187" t="n">
-        <v>0.01775170645816494</v>
+        <v>0.0546912843268907</v>
       </c>
       <c r="E187" t="n">
         <v>1024</v>
@@ -12243,13 +12243,13 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>0.1489597780859917</v>
+        <v>0.1036468330134357</v>
       </c>
       <c r="C188" t="n">
-        <v>0.01929036607842895</v>
+        <v>0.00350036847393256</v>
       </c>
       <c r="D188" t="n">
-        <v>0.03201205427642138</v>
+        <v>0.05769381581662567</v>
       </c>
       <c r="E188" t="n">
         <v>1024</v>
@@ -12306,13 +12306,13 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>0.2929264909847434</v>
+        <v>0.1042866282789507</v>
       </c>
       <c r="C189" t="n">
-        <v>0.141881572770248</v>
+        <v>0.005017931567306684</v>
       </c>
       <c r="D189" t="n">
-        <v>0.1199921526198232</v>
+        <v>0.07039515584616313</v>
       </c>
       <c r="E189" t="n">
         <v>1024</v>
@@ -12369,13 +12369,13 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>0.3900138696255201</v>
+        <v>0.109404990403071</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2454871150871148</v>
+        <v>0.002995479868848574</v>
       </c>
       <c r="D190" t="n">
-        <v>0.2588298046386155</v>
+        <v>0.06840902256538317</v>
       </c>
       <c r="E190" t="n">
         <v>1024</v>
@@ -12432,13 +12432,13 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>0.3578363384188627</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C191" t="n">
-        <v>0.105582741664807</v>
+        <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>0.1392414809040409</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
         <v>1024</v>
@@ -12495,7 +12495,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -12558,7 +12558,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>0.3134535367545077</v>
+        <v>0.09468969929622521</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>

--- a/grid_search_results.xlsx
+++ b/grid_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,23 +525,23 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.454336147352264</v>
+        <v>0.5947736474052263</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1008942293059586</v>
+        <v>0.5007231513175382</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2656927395394891</v>
+        <v>0.6638029905466035</v>
       </c>
       <c r="E2" t="n">
         <v>512</v>
       </c>
       <c r="F2" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ReLU</t>
+          <t>Tanh</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>0.001</v>
@@ -574,13 +574,454 @@
         <v>10000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="R2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3433934486566065</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tanh</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.001</v>
       </c>
-      <c r="S2" t="n">
-        <v>16</v>
+      <c r="K3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>300</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3433934486566065</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>512</v>
+      </c>
+      <c r="F4" t="n">
+        <v>128</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tanh</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>800</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3433934486566065</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>512</v>
+      </c>
+      <c r="F5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tanh</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>800</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S5" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3441295546558704</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-5.577500919994737e-05</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.001362628683158369</v>
+      </c>
+      <c r="E6" t="n">
+        <v>512</v>
+      </c>
+      <c r="F6" t="n">
+        <v>128</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ReLU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>300</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.3433934486566065</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>512</v>
+      </c>
+      <c r="F7" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ReLU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>300</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5947736474052263</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5003233885299796</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6618889737323401</v>
+      </c>
+      <c r="E8" t="n">
+        <v>512</v>
+      </c>
+      <c r="F8" t="n">
+        <v>128</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ReLU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>800</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3433934486566065</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>512</v>
+      </c>
+      <c r="F9" t="n">
+        <v>128</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ReLU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>800</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
